--- a/artfynd/A 63440-2025 artfynd.xlsx
+++ b/artfynd/A 63440-2025 artfynd.xlsx
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>

--- a/artfynd/A 63440-2025 artfynd.xlsx
+++ b/artfynd/A 63440-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794742</v>
+        <v>128789817</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tansväggen V, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499863</v>
+        <v>500084</v>
       </c>
       <c r="R2" t="n">
-        <v>6692042</v>
+        <v>6692473</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,29 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794698</v>
+        <v>128794783</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499856</v>
+        <v>499864</v>
       </c>
       <c r="R3" t="n">
-        <v>6692021</v>
+        <v>6692056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -850,6 +846,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,48 +878,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794725</v>
+        <v>61455550</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>88953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violett fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Clavaria amethystina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Holmsk.) Bull.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tansväggen V, Dlr</t>
+          <t>Älgtorpet, Tansväggarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499872</v>
+        <v>499935</v>
       </c>
       <c r="R4" t="n">
-        <v>6692022</v>
+        <v>6692207</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -945,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2016-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2016-08-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,25 +971,35 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal betesmark numera klippt gräsmark</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Frida Hellsing</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Frida Hellsing</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128789816</v>
+        <v>128789828</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499873</v>
+        <v>500013</v>
       </c>
       <c r="R5" t="n">
-        <v>6692072</v>
+        <v>6692185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,48 +1093,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794783</v>
+        <v>61455824</v>
       </c>
       <c r="B6" t="n">
-        <v>91491</v>
+        <v>88964</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>3279</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Maskfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Clavaria fragilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Holmsk., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tansväggen V, Dlr</t>
+          <t>Älgtorpet, Tansväggarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499864</v>
+        <v>499935</v>
       </c>
       <c r="R6" t="n">
-        <v>6692056</v>
+        <v>6692207</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1148,17 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2016-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På asplåga.</t>
+          <t>2016-08-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,63 +1186,73 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal betesmark numera klippt gräsmark,</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Frida Hellsing</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Frida Hellsing</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128789818</v>
+        <v>128778780</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>89081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4374</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tansväggen V, Dlr</t>
+          <t>Älgtorpet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499781</v>
+        <v>499933</v>
       </c>
       <c r="R7" t="n">
-        <v>6692106</v>
+        <v>6692215</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,14 +1279,19 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosök kraftiga hack.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,17 +1311,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794759</v>
+        <v>128778807</v>
       </c>
       <c r="B8" t="n">
-        <v>80175</v>
+        <v>89029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,40 +1329,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>4392</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tansväggen V, Dlr</t>
+          <t>Älgtorpet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499842</v>
+        <v>499933</v>
       </c>
       <c r="R8" t="n">
-        <v>6692043</v>
+        <v>6692215</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,40 +1382,49 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128789819</v>
+        <v>128789813</v>
       </c>
       <c r="B9" t="n">
-        <v>80050</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1432,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499809</v>
+        <v>500121</v>
       </c>
       <c r="R9" t="n">
-        <v>6692123</v>
+        <v>6692454</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,11 +1492,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal aspstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,32 +1518,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128789824</v>
+        <v>128789826</v>
       </c>
       <c r="B10" t="n">
-        <v>91558</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499826</v>
+        <v>499969</v>
       </c>
       <c r="R10" t="n">
-        <v>6692079</v>
+        <v>6692326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,11 +1618,11 @@
         <v>128789827</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1685,14 +1712,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794717</v>
+        <v>128794698</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1723,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499863</v>
+        <v>499856</v>
       </c>
       <c r="R12" t="n">
-        <v>6692006</v>
+        <v>6692021</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1786,48 +1813,51 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128789822</v>
+        <v>128794717</v>
       </c>
       <c r="B13" t="n">
-        <v>91558</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tansväggen V, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499792</v>
+        <v>499863</v>
       </c>
       <c r="R13" t="n">
-        <v>6692094</v>
+        <v>6692006</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1865,66 +1895,70 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128789823</v>
+        <v>128794725</v>
       </c>
       <c r="B14" t="n">
-        <v>91558</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tansväggen V, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499783</v>
+        <v>499872</v>
       </c>
       <c r="R14" t="n">
-        <v>6692114</v>
+        <v>6692022</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1962,32 +1996,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794846</v>
+        <v>128794742</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2018,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500063</v>
+        <v>499863</v>
       </c>
       <c r="R15" t="n">
-        <v>6692315</v>
+        <v>6692042</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2081,42 +2116,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128789814</v>
+        <v>128794796</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2124,13 +2154,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500085</v>
+        <v>499981</v>
       </c>
       <c r="R16" t="n">
-        <v>6692458</v>
+        <v>6692388</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2162,43 +2192,39 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spår av barkfläkning här och där i omr. Troligt av tretåig.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794796</v>
+        <v>128794808</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2229,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499981</v>
+        <v>499985</v>
       </c>
       <c r="R17" t="n">
-        <v>6692388</v>
+        <v>6692373</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2292,48 +2318,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128789813</v>
+        <v>128794831</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tansväggen V, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500121</v>
+        <v>500068</v>
       </c>
       <c r="R18" t="n">
-        <v>6692454</v>
+        <v>6692351</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2371,60 +2400,56 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128789815</v>
+        <v>128794846</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2432,13 +2457,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500034</v>
+        <v>500063</v>
       </c>
       <c r="R19" t="n">
-        <v>6692065</v>
+        <v>6692315</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2470,77 +2495,76 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på äldre stor tall.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128789817</v>
+        <v>128794853</v>
       </c>
       <c r="B20" t="n">
-        <v>91491</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tansväggen V, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500084</v>
+        <v>500052</v>
       </c>
       <c r="R20" t="n">
-        <v>6692473</v>
+        <v>6692325</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2578,32 +2602,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794831</v>
+        <v>128794863</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2634,10 +2659,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500068</v>
+        <v>500061</v>
       </c>
       <c r="R21" t="n">
-        <v>6692351</v>
+        <v>6692299</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2697,51 +2722,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128794863</v>
+        <v>128789819</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tansväggen V, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500061</v>
+        <v>499809</v>
       </c>
       <c r="R22" t="n">
-        <v>6692299</v>
+        <v>6692123</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2773,57 +2795,61 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal aspstubbe.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128794853</v>
+        <v>128794759</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2836,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500052</v>
+        <v>499842</v>
       </c>
       <c r="R23" t="n">
-        <v>6692325</v>
+        <v>6692043</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2899,51 +2925,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794808</v>
+        <v>128789818</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tansväggen V, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499985</v>
+        <v>499781</v>
       </c>
       <c r="R24" t="n">
-        <v>6692373</v>
+        <v>6692106</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2975,70 +2998,82 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Födosök kraftiga hack.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128789821</v>
+        <v>128789814</v>
       </c>
       <c r="B25" t="n">
-        <v>80106</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tansväggen V, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500126</v>
+        <v>500085</v>
       </c>
       <c r="R25" t="n">
-        <v>6692467</v>
+        <v>6692458</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3075,14 +3110,14 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Spår av barkfläkning här och där i omr. Troligt av tretåig.</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3099,6 +3134,538 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128789815</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tansväggen V, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>500034</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6692065</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på äldre stor tall.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128789816</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tansväggen V, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>499873</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6692072</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>66741054</v>
+      </c>
+      <c r="B28" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Älgtorpet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>499937</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6692198</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2017-07-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2017-07-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16490806</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Älgtorpet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>499937</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6692198</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128789821</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tansväggen V, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>500126</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6692467</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63440-2025 artfynd.xlsx
+++ b/artfynd/A 63440-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789817</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61455550</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789828</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61455824</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778780</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778807</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789813</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789826</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,6 +1759,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789827</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794698</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1911,6 +1971,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794717</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2012,6 +2077,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794725</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2113,6 +2183,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794742</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2214,6 +2289,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794796</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2315,6 +2395,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794808</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,6 +2501,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794831</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794846</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2618,6 +2713,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794853</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794863</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2821,6 +2926,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789819</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2922,6 +3032,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794759</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3024,6 +3139,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789818</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3134,6 +3254,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789814</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3244,6 +3369,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789815</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3346,6 +3476,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789816</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3452,6 +3587,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66741054</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3564,6 +3704,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16490806</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3666,8 +3811,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789821</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>